--- a/naver-place-crawler/results_health/서대문_PT.xlsx
+++ b/naver-place-crawler/results_health/서대문_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>오버탑휘트니스&amp;필라테스 가좌점</t>
+          <t>휘트니스엠 충정로점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>haon8312@naver.com</t>
+          <t>fitnessm17@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1306-2858</t>
+          <t>0507-1394-0801</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로 56 지하1층 B01,B02, B03, B04, B05 호</t>
+          <t>서울 중구 서소문로 38 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xmBrxexj</t>
+          <t>https://blog.naver.com/fitnessm17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wqhojnt</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>327</v>
+        <v>381</v>
       </c>
       <c r="Q2" t="n">
-        <v>180</v>
+        <v>62</v>
       </c>
       <c r="R2" t="n">
-        <v>507</v>
+        <v>443</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1488986101</t>
+          <t>2042672655</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488986101</t>
+          <t>https://m.place.naver.com/place/2042672655</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="Q3" t="n">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="R3" t="n">
-        <v>1636</v>
+        <v>1647</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="Q4" t="n">
-        <v>1097</v>
+        <v>1078</v>
       </c>
       <c r="R4" t="n">
-        <v>1759</v>
+        <v>1744</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>이태원짐 서대문구청점</t>
+          <t>1986피트니스 헬스PT 무악재점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>itaewongym2@naver.com</t>
+          <t>1986fitness5@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1335-4180</t>
+          <t>0507-1443-1986</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 286 2층</t>
+          <t>서울특별시 서대문구 통일로 339 B층 301호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewongym2</t>
+          <t>https://blog.naver.com/1986fitness5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>635</v>
+        <v>1955</v>
       </c>
       <c r="Q5" t="n">
-        <v>208</v>
+        <v>1522</v>
       </c>
       <c r="R5" t="n">
-        <v>843</v>
+        <v>3477</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1853970001</t>
+          <t>1220265026</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853970001</t>
+          <t>https://m.place.naver.com/place/1220265026</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 무악재점</t>
+          <t>이태원짐 서대문구청점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1986fitness5@naver.com</t>
+          <t>itaewongym2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1443-1986</t>
+          <t>0507-1335-4180</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 339 B층 301호</t>
+          <t>서울특별시 서대문구 연희로 286 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness5</t>
+          <t>https://blog.naver.com/itaewongym2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1942</v>
+        <v>643</v>
       </c>
       <c r="Q6" t="n">
-        <v>1488</v>
+        <v>210</v>
       </c>
       <c r="R6" t="n">
-        <v>3430</v>
+        <v>853</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1220265026</t>
+          <t>1853970001</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220265026</t>
+          <t>https://m.place.naver.com/place/1853970001</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오늘부터핏 PT</t>
+          <t>셀프메이드짐 연희</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>randomsss@naver.com</t>
+          <t>selfmadegym2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1412-3111</t>
+          <t>0507-1360-5190</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 이화여대2길 10 일홍빌딩 3층</t>
+          <t>서울특별시 서대문구 연희로 185 B1 셀프메이드짐 연희</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/randomsss/222899508551</t>
+          <t>https://blog.naver.com/selfmadegym2/223397334694</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>521</v>
+        <v>652</v>
       </c>
       <c r="Q7" t="n">
-        <v>1741</v>
+        <v>1749</v>
       </c>
       <c r="R7" t="n">
-        <v>2262</v>
+        <v>2401</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1110,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1795503434</t>
+          <t>1382051925</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1795503434</t>
+          <t>https://m.place.naver.com/place/1382051925</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피티루트 홍제 무악재점</t>
+          <t>짐티피 연희점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hayama89@naver.com</t>
+          <t>gymtipi5@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1343-0653</t>
+          <t>0507-1411-0572</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 360 보하빌딩 6층 피티루트</t>
+          <t>서울특별시 서대문구 연희로25길 18 지하 1층(연희동, 대화 빌딩)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pt_root</t>
+          <t>https://blog.naver.com/gymtipi5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>124</v>
+        <v>502</v>
       </c>
       <c r="Q8" t="n">
-        <v>277</v>
+        <v>495</v>
       </c>
       <c r="R8" t="n">
-        <v>401</v>
+        <v>997</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,47 +1204,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1191919965</t>
+          <t>1530671650</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1191919965</t>
+          <t>https://m.place.naver.com/place/1530671650</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아벨라 PT&amp; 필라테스 서대문역점</t>
+          <t>피티루트 홍제 무악재점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abella11@naver.com</t>
+          <t>hayama89@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1343-0653</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 177 4층</t>
+          <t>서울특별시 서대문구 통일로 360 보하빌딩 6층 피티루트</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/abella_pt_pillates_?igsh=MXBnN2xza3R3aGk4bA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/pt_root</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>236</v>
+        <v>124</v>
       </c>
       <c r="Q9" t="n">
-        <v>218</v>
+        <v>278</v>
       </c>
       <c r="R9" t="n">
-        <v>454</v>
+        <v>402</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1027229578</t>
+          <t>1191919965</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027229578</t>
+          <t>https://m.place.naver.com/place/1191919965</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엠베이스짐 가재울점</t>
+          <t>수 피티 연희점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mbasegym@naver.com</t>
+          <t>lovedaisy78@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1442-2222</t>
+          <t>0507-1438-8791</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로 56 성공타워 6층 608호 엠베이스짐</t>
+          <t>서울특별시 서대문구 연희로 81-21 6층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mbasegym</t>
+          <t>https://www.instagram.com/sufit.ness</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="R10" t="n">
-        <v>30</v>
+        <v>266</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,51 +1392,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37294107</t>
+          <t>1060397560</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37294107</t>
+          <t>https://m.place.naver.com/place/1060397560</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스타칼리휘트니스 연희점</t>
+          <t>모브플렉스 웰니스클럽 북가좌점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>starkalibest@naver.com</t>
+          <t>movflex@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1328-4477</t>
+          <t>0507-1465-5212</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 82 브라운스톤 연희 B1</t>
+          <t>서울 서대문구 응암로 118 C동 0층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_gknKT/chat</t>
+          <t>https://www.movflex.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1448,13 +1456,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsjq5zj</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>273</v>
+        <v>206</v>
       </c>
       <c r="Q11" t="n">
-        <v>371</v>
+        <v>45</v>
       </c>
       <c r="R11" t="n">
-        <v>644</v>
+        <v>251</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1490,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>31044421</t>
+          <t>1920908511</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31044421</t>
+          <t>https://m.place.naver.com/place/1920908511</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서대문_PT.xlsx
+++ b/naver-place-crawler/results_health/서대문_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q2" t="n">
         <v>62</v>
       </c>
       <c r="R2" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="Q3" t="n">
         <v>817</v>
       </c>
       <c r="R3" t="n">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -816,10 +816,10 @@
         <v>666</v>
       </c>
       <c r="Q4" t="n">
-        <v>1078</v>
+        <v>1088</v>
       </c>
       <c r="R4" t="n">
-        <v>1744</v>
+        <v>1754</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1955</v>
+        <v>1959</v>
       </c>
       <c r="Q5" t="n">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="R5" t="n">
-        <v>3477</v>
+        <v>3482</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>셀프메이드짐 연희</t>
+          <t>바디채널&amp;히트35 신촌이대역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>selfmadegym2@naver.com</t>
+          <t>bodych36@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1360-5190</t>
+          <t>0507-1473-2117</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 185 B1 셀프메이드짐 연희</t>
+          <t>서울특별시 서대문구 신촌로 155 해암빌딩 3층, 4층 바디채널</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/selfmadegym2/223397334694</t>
+          <t>https://blog.naver.com/bodych36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>652</v>
+        <v>572</v>
       </c>
       <c r="Q7" t="n">
-        <v>1749</v>
+        <v>339</v>
       </c>
       <c r="R7" t="n">
-        <v>2401</v>
+        <v>911</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1382051925</t>
+          <t>1485878804</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382051925</t>
+          <t>https://m.place.naver.com/place/1485878804</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Q8" t="n">
         <v>495</v>
       </c>
       <c r="R8" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1286,10 +1286,10 @@
         <v>124</v>
       </c>
       <c r="Q9" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="R9" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1308,41 +1308,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>수 피티 연희점</t>
+          <t>크로스핏 런신촌</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lovedaisy78@naver.com</t>
+          <t>projectfithouse@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1438-8791</t>
+          <t>0507-1365-1825</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 81-21 6층</t>
+          <t>서울특별시 서대문구 연세로9길 37 지하 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sufit.ness</t>
+          <t>https://www.projectrun.co.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="Q10" t="n">
-        <v>147</v>
+        <v>241</v>
       </c>
       <c r="R10" t="n">
-        <v>266</v>
+        <v>434</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1060397560</t>
+          <t>1720233681</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060397560</t>
+          <t>https://m.place.naver.com/place/1720233681</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1414,34 +1414,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모브플렉스 웰니스클럽 북가좌점</t>
+          <t>수 피티 연희점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>movflex@naver.com</t>
+          <t>lovedaisy78@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1465-5212</t>
+          <t>0507-1438-8791</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 서대문구 응암로 118 C동 0층</t>
+          <t>서울특별시 서대문구 연희로 81-21 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.movflex.co.kr</t>
+          <t>https://www.instagram.com/sufit.ness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1456,14 +1456,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsjq5zj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1475,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="Q11" t="n">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="R11" t="n">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1920908511</t>
+          <t>1060397560</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920908511</t>
+          <t>https://m.place.naver.com/place/1060397560</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서대문_PT.xlsx
+++ b/naver-place-crawler/results_health/서대문_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 397 한신휴플러스 상가 2층 309호</t>
+          <t>서울 서대문구 통일로 397 한신휴플러스 상가 2층 309호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qwpv</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>홀리핏 신촌점</t>
+          <t>1986피트니스 헬스PT 무악재점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ycy06177@naver.com</t>
+          <t>1986fitness5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1409-9915</t>
+          <t>0507-1443-1986</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물1길 16 1층~4층</t>
+          <t>서울 서대문구 통일로 339 B층 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ycy06177</t>
+          <t>https://blog.naver.com/1986fitness5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -798,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4szvi</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>666</v>
+        <v>1959</v>
       </c>
       <c r="Q4" t="n">
-        <v>1088</v>
+        <v>1524</v>
       </c>
       <c r="R4" t="n">
-        <v>1754</v>
+        <v>3483</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1703343634</t>
+          <t>1220265026</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1703343634</t>
+          <t>https://m.place.naver.com/place/1220265026</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 무악재점</t>
+          <t>홀리핏 신촌점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1986fitness5@naver.com</t>
+          <t>ycy06177@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1443-1986</t>
+          <t>0507-1409-9915</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 339 B층 301호</t>
+          <t>서울 서대문구 명물1길 16 1층~4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness5</t>
+          <t>https://blog.naver.com/ycy06177</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4c2rj</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1959</v>
+        <v>666</v>
       </c>
       <c r="Q5" t="n">
-        <v>1523</v>
+        <v>1090</v>
       </c>
       <c r="R5" t="n">
-        <v>3482</v>
+        <v>1756</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1220265026</t>
+          <t>1703343634</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220265026</t>
+          <t>https://m.place.naver.com/place/1703343634</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -961,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 286 2층</t>
+          <t>서울 서대문구 연희로 286 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fh3o</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1055,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 신촌로 155 해암빌딩 3층, 4층 바디채널</t>
+          <t>서울 서대문구 신촌로 155 해암빌딩 3층, 4층 바디채널</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1080,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46zbh</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1149,7 +1169,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로25길 18 지하 1층(연희동, 대화 빌딩)</t>
+          <t>서울 서대문구 연희로25길 18 지하 1층(연희동, 대화 빌딩)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1174,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9xflz1</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1243,7 +1267,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 360 보하빌딩 6층 피티루트</t>
+          <t>서울 서대문구 통일로 360 보하빌딩 6층 피티루트</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4etr7</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1337,7 +1365,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로9길 37 지하 1층</t>
+          <t>서울 서대문구 연세로9길 37 지하 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1362,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v76c</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1431,7 +1463,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 81-21 6층</t>
+          <t>서울 서대문구 연희로 81-21 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1456,10 +1488,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qp0x</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/서대문_PT.xlsx
+++ b/naver-place-crawler/results_health/서대문_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 중구 서소문로 38 지하1층</t>
+          <t>서울특별시 중구 서소문로 38 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wqhojnt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q2" t="n">
         <v>62</v>
       </c>
       <c r="R2" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 서대문구 통일로 397 한신휴플러스 상가 2층 309호</t>
+          <t>서울특별시 서대문구 통일로 397 한신휴플러스 상가 2층 309호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qwpv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 무악재점</t>
+          <t>홀리핏 신촌점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1986fitness5@naver.com</t>
+          <t>ycy06177@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1443-1986</t>
+          <t>0507-1409-9915</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울 서대문구 통일로 339 B층 301호</t>
+          <t>서울특별시 서대문구 명물1길 16 1층~4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness5</t>
+          <t>https://blog.naver.com/ycy06177</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4szvi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1959</v>
+        <v>666</v>
       </c>
       <c r="Q4" t="n">
-        <v>1524</v>
+        <v>1089</v>
       </c>
       <c r="R4" t="n">
-        <v>3483</v>
+        <v>1755</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1220265026</t>
+          <t>1703343634</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220265026</t>
+          <t>https://m.place.naver.com/place/1703343634</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>홀리핏 신촌점</t>
+          <t>1986피트니스 헬스PT 무악재점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ycy06177@naver.com</t>
+          <t>1986fitness5@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1409-9915</t>
+          <t>0507-1443-1986</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울 서대문구 명물1길 16 1층~4층</t>
+          <t>서울특별시 서대문구 통일로 339 B층 301호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ycy06177</t>
+          <t>https://blog.naver.com/1986fitness5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4c2rj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>666</v>
+        <v>1963</v>
       </c>
       <c r="Q5" t="n">
-        <v>1090</v>
+        <v>1524</v>
       </c>
       <c r="R5" t="n">
-        <v>1756</v>
+        <v>3487</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1703343634</t>
+          <t>1220265026</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1703343634</t>
+          <t>https://m.place.naver.com/place/1220265026</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울 서대문구 연희로 286 2층</t>
+          <t>서울특별시 서대문구 연희로 286 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fh3o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1054,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바디채널&amp;히트35 신촌이대역점</t>
+          <t>셀프메이드짐 연희</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodych36@naver.com</t>
+          <t>selfmadegym2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1473-2117</t>
+          <t>0507-1360-5190</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울 서대문구 신촌로 155 해암빌딩 3층, 4층 바디채널</t>
+          <t>서울특별시 서대문구 연희로 185 B1 셀프메이드짐 연희</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodych36</t>
+          <t>https://blog.naver.com/selfmadegym2/223397334694</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1096,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46zbh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>572</v>
+        <v>655</v>
       </c>
       <c r="Q7" t="n">
-        <v>339</v>
+        <v>1751</v>
       </c>
       <c r="R7" t="n">
-        <v>911</v>
+        <v>2406</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1485878804</t>
+          <t>1382051925</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485878804</t>
+          <t>https://m.place.naver.com/place/1382051925</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1147,34 +1123,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>짐티피 연희점</t>
+          <t>피티루트 홍제 무악재점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gymtipi5@naver.com</t>
+          <t>hayama89@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1411-0572</t>
+          <t>0507-1343-0653</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 서대문구 연희로25길 18 지하 1층(연희동, 대화 빌딩)</t>
+          <t>서울특별시 서대문구 통일로 360 보하빌딩 6층 피티루트</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymtipi5</t>
+          <t>https://www.instagram.com/pt_root</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,19 +1165,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9xflz1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>503</v>
+        <v>124</v>
       </c>
       <c r="Q8" t="n">
-        <v>495</v>
+        <v>279</v>
       </c>
       <c r="R8" t="n">
-        <v>998</v>
+        <v>403</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1530671650</t>
+          <t>1191919965</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1530671650</t>
+          <t>https://m.place.naver.com/place/1191919965</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피티루트 홍제 무악재점</t>
+          <t>수 피티 연희점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hayama89@naver.com</t>
+          <t>lovedaisy78@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1343-0653</t>
+          <t>0507-1438-8791</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 서대문구 통일로 360 보하빌딩 6층 피티루트</t>
+          <t>서울특별시 서대문구 연희로 81-21 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pt_root</t>
+          <t>https://www.instagram.com/sufit.ness</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1292,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4etr7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="Q9" t="n">
-        <v>279</v>
+        <v>147</v>
       </c>
       <c r="R9" t="n">
-        <v>403</v>
+        <v>266</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1191919965</t>
+          <t>1060397560</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1191919965</t>
+          <t>https://m.place.naver.com/place/1060397560</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,39 +1311,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>크로스핏 런신촌</t>
+          <t>모브플렉스 웰니스클럽 북가좌점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>projectfithouse@naver.com</t>
+          <t>movflex@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1365-1825</t>
+          <t>0507-1465-5212</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 서대문구 연세로9길 37 지하 1층</t>
+          <t>서울 서대문구 응암로 118 C동 0층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.projectrun.co.kr</t>
+          <t>https://www.movflex.co.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1363,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v76c</t>
+          <t>https://talk.naver.com/ct/wsjq5zj</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="Q10" t="n">
-        <v>241</v>
+        <v>45</v>
       </c>
       <c r="R10" t="n">
-        <v>434</v>
+        <v>255</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1720233681</t>
+          <t>1920908511</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720233681</t>
+          <t>https://m.place.naver.com/place/1920908511</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>수 피티 연희점</t>
+          <t>엠베이스짐 가재울점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lovedaisy78@naver.com</t>
+          <t>mbasegym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1438-8791</t>
+          <t>0507-1442-2222</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 서대문구 연희로 81-21 6층</t>
+          <t>서울특별시 서대문구 수색로 56 성공타워 6층 608호 엠베이스짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sufit.ness</t>
+          <t>https://blog.naver.com/mbasegym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,19 +1451,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qp0x</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1507,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
-        <v>266</v>
+        <v>30</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1060397560</t>
+          <t>37294107</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060397560</t>
+          <t>https://m.place.naver.com/place/37294107</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/서대문_PT.xlsx
+++ b/naver-place-crawler/results_health/서대문_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>휘트니스엠 충정로점</t>
+          <t>잇바디휘트니스 홍제점 헬스 PT 필라테스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fitnessm17@naver.com</t>
+          <t>itbodyfitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1394-0801</t>
+          <t>0507-1301-7016</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 38 지하1층</t>
+          <t>서울특별시 서대문구 통일로 397 한신휴플러스 상가 2층 309호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessm17</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,23 +596,27 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qwpv</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>386</v>
+        <v>831</v>
       </c>
       <c r="Q2" t="n">
-        <v>62</v>
+        <v>817</v>
       </c>
       <c r="R2" t="n">
-        <v>448</v>
+        <v>1648</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2042672655</t>
+          <t>13478870</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042672655</t>
+          <t>https://m.place.naver.com/place/13478870</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>잇바디휘트니스 홍제점 헬스 PT 필라테스</t>
+          <t>홀리핏 신촌점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>itbodyfitness@naver.com</t>
+          <t>ycy06177@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1301-7016</t>
+          <t>0507-1409-9915</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 397 한신휴플러스 상가 2층 309호</t>
+          <t>서울특별시 서대문구 명물1길 16 1층~4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itbodyfitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,23 +694,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4c2rj</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>831</v>
+        <v>667</v>
       </c>
       <c r="Q3" t="n">
-        <v>817</v>
+        <v>1095</v>
       </c>
       <c r="R3" t="n">
-        <v>1648</v>
+        <v>1762</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13478870</t>
+          <t>1703343634</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13478870</t>
+          <t>https://m.place.naver.com/place/1703343634</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>홀리핏 신촌점</t>
+          <t>1986피트니스 헬스PT 무악재점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ycy06177@naver.com</t>
+          <t>1986fitness5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1409-9915</t>
+          <t>0507-1443-1986</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물1길 16 1층~4층</t>
+          <t>서울특별시 서대문구 통일로 339 B층 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ycy06177</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +792,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4szvi</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>666</v>
+        <v>1964</v>
       </c>
       <c r="Q4" t="n">
-        <v>1089</v>
+        <v>1525</v>
       </c>
       <c r="R4" t="n">
-        <v>1755</v>
+        <v>3489</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1703343634</t>
+          <t>1220265026</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1703343634</t>
+          <t>https://m.place.naver.com/place/1220265026</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 무악재점</t>
+          <t>이태원짐 서대문구청점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1986fitness5@naver.com</t>
+          <t>itaewongym2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1443-1986</t>
+          <t>0507-1335-4180</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 339 B층 301호</t>
+          <t>서울특별시 서대문구 연희로 286 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,20 +890,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fh3o</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1963</v>
+        <v>643</v>
       </c>
       <c r="Q5" t="n">
-        <v>1524</v>
+        <v>210</v>
       </c>
       <c r="R5" t="n">
-        <v>3487</v>
+        <v>853</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1220265026</t>
+          <t>1853970001</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220265026</t>
+          <t>https://m.place.naver.com/place/1853970001</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이태원짐 서대문구청점</t>
+          <t>셀프메이드짐 연희</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>itaewongym2@naver.com</t>
+          <t>selfmadegym02@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1335-4180</t>
+          <t>0507-1360-5190</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 286 2층</t>
+          <t>서울특별시 서대문구 연희로 185 B1 셀프메이드짐 연희</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewongym2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +988,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4736t</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="Q6" t="n">
-        <v>210</v>
+        <v>1751</v>
       </c>
       <c r="R6" t="n">
-        <v>853</v>
+        <v>2406</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1853970001</t>
+          <t>1382051925</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853970001</t>
+          <t>https://m.place.naver.com/place/1382051925</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>셀프메이드짐 연희</t>
+          <t>수 피티 연희점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>selfmadegym2@naver.com</t>
+          <t>lovedaisy78@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1360-5190</t>
+          <t>0507-1438-8791</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 185 B1 셀프메이드짐 연희</t>
+          <t>서울특별시 서대문구 연희로 81-21 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/selfmadegym2/223397334694</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,20 +1086,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qp0x</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>655</v>
+        <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>1751</v>
+        <v>147</v>
       </c>
       <c r="R7" t="n">
-        <v>2406</v>
+        <v>266</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1382051925</t>
+          <t>1060397560</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382051925</t>
+          <t>https://m.place.naver.com/place/1060397560</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피티루트 홍제 무악재점</t>
+          <t>모브플렉스 웰니스클럽 북가좌점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hayama89@naver.com</t>
+          <t>movflex@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1343-0653</t>
+          <t>0507-1465-5212</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 360 보하빌딩 6층 피티루트</t>
+          <t>서울 서대문구 응암로 118 C동 0층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pt_root</t>
+          <t>https://www.movflex.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsjq5zj</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="Q8" t="n">
-        <v>279</v>
+        <v>45</v>
       </c>
       <c r="R8" t="n">
-        <v>403</v>
+        <v>256</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1191919965</t>
+          <t>1920908511</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1191919965</t>
+          <t>https://m.place.naver.com/place/1920908511</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>수 피티 연희점</t>
+          <t>엠베이스짐 가재울점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lovedaisy78@naver.com</t>
+          <t>mbasegym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1438-8791</t>
+          <t>0507-1442-2222</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 81-21 6층</t>
+          <t>서울특별시 서대문구 수색로 56 성공타워 6층 608호 엠베이스짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sufit.ness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1264,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc3rb1</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="Q9" t="n">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="R9" t="n">
-        <v>266</v>
+        <v>30</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1060397560</t>
+          <t>37294107</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060397560</t>
+          <t>https://m.place.naver.com/place/37294107</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,44 +1343,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모브플렉스 웰니스클럽 북가좌점</t>
+          <t>스타칼리휘트니스 연희점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>movflex@naver.com</t>
+          <t>starkalibest@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1465-5212</t>
+          <t>0507-1328-4477</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 서대문구 응암로 118 C동 0층</t>
+          <t>서울특별시 서대문구 연희로 82 브라운스톤 연희 B1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.movflex.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1363,12 +1395,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wsjq5zj</t>
+          <t>https://talk.naver.com/ct/w5y1bb</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1377,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>210</v>
+        <v>276</v>
       </c>
       <c r="Q10" t="n">
-        <v>45</v>
+        <v>372</v>
       </c>
       <c r="R10" t="n">
-        <v>255</v>
+        <v>648</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,109 +1424,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1920908511</t>
+          <t>31044421</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920908511</t>
+          <t>https://m.place.naver.com/place/31044421</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>엠베이스짐 가재울점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>mbasegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1442-2222</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>서울특별시 서대문구 수색로 56 성공타워 6층 608호 엠베이스짐</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/mbasegym</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>17</v>
-      </c>
-      <c r="R11" t="n">
-        <v>30</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>37294107</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37294107</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/서대문_PT.xlsx
+++ b/naver-place-crawler/results_health/서대문_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>잇바디휘트니스 홍제점 헬스 PT 필라테스</t>
+          <t>휘트니스엠 충정로점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>itbodyfitness@naver.com</t>
+          <t>fitnessm17@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1301-7016</t>
+          <t>0507-1394-0801</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 397 한신휴플러스 상가 2층 309호</t>
+          <t>서울 중구 서소문로 38 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitnessm17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4qwpv</t>
+          <t>https://talk.naver.com/ct/wqhojnt</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>831</v>
+        <v>388</v>
       </c>
       <c r="Q2" t="n">
-        <v>817</v>
+        <v>62</v>
       </c>
       <c r="R2" t="n">
-        <v>1648</v>
+        <v>450</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13478870</t>
+          <t>2042672655</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13478870</t>
+          <t>https://m.place.naver.com/place/2042672655</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>홀리핏 신촌점</t>
+          <t>잇바디휘트니스 홍제점 헬스 PT 필라테스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ycy06177@naver.com</t>
+          <t>itbodyfitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1409-9915</t>
+          <t>0507-1301-7016</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물1길 16 1층~4층</t>
+          <t>서울특별시 서대문구 통일로 397 한신휴플러스 상가 2층 309호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/itbodyfitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,27 +694,23 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4c2rj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>667</v>
+        <v>831</v>
       </c>
       <c r="Q3" t="n">
-        <v>1095</v>
+        <v>817</v>
       </c>
       <c r="R3" t="n">
-        <v>1762</v>
+        <v>1648</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1703343634</t>
+          <t>13478870</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1703343634</t>
+          <t>https://m.place.naver.com/place/13478870</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 무악재점</t>
+          <t>홀리핏 신촌점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1986fitness5@naver.com</t>
+          <t>ycy06177@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1443-1986</t>
+          <t>0507-1409-9915</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 339 B층 301호</t>
+          <t>서울특별시 서대문구 명물1길 16 1층~4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ycy06177</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,24 +788,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4szvi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1964</v>
+        <v>667</v>
       </c>
       <c r="Q4" t="n">
-        <v>1525</v>
+        <v>1095</v>
       </c>
       <c r="R4" t="n">
-        <v>3489</v>
+        <v>1762</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1220265026</t>
+          <t>1703343634</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220265026</t>
+          <t>https://m.place.naver.com/place/1703343634</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>이태원짐 서대문구청점</t>
+          <t>1986피트니스 헬스PT 무악재점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>itaewongym2@naver.com</t>
+          <t>1986fitness5@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1335-4180</t>
+          <t>0507-1443-1986</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 286 2층</t>
+          <t>서울특별시 서대문구 통일로 339 B층 301호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/1986fitness5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,24 +882,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fh3o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>643</v>
+        <v>1964</v>
       </c>
       <c r="Q5" t="n">
-        <v>210</v>
+        <v>1525</v>
       </c>
       <c r="R5" t="n">
-        <v>853</v>
+        <v>3489</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1853970001</t>
+          <t>1220265026</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853970001</t>
+          <t>https://m.place.naver.com/place/1220265026</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -956,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>셀프메이드짐 연희</t>
+          <t>이태원짐 서대문구청점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>selfmadegym02@naver.com</t>
+          <t>itaewongym2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1360-5190</t>
+          <t>0507-1335-4180</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 185 B1 셀프메이드짐 연희</t>
+          <t>서울특별시 서대문구 연희로 286 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/itaewongym2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,24 +976,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4736t</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="Q6" t="n">
-        <v>1751</v>
+        <v>210</v>
       </c>
       <c r="R6" t="n">
-        <v>2406</v>
+        <v>853</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1382051925</t>
+          <t>1853970001</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382051925</t>
+          <t>https://m.place.naver.com/place/1853970001</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>수 피티 연희점</t>
+          <t>셀프메이드짐 연희</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lovedaisy78@naver.com</t>
+          <t>selfmadegym2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1438-8791</t>
+          <t>0507-1360-5190</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 81-21 6층</t>
+          <t>서울특별시 서대문구 연희로 185 B1 셀프메이드짐 연희</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/selfmadegym2/223397334694</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,24 +1070,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qp0x</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>119</v>
+        <v>655</v>
       </c>
       <c r="Q7" t="n">
-        <v>147</v>
+        <v>1751</v>
       </c>
       <c r="R7" t="n">
-        <v>266</v>
+        <v>2406</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,56 +1110,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1060397560</t>
+          <t>1382051925</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060397560</t>
+          <t>https://m.place.naver.com/place/1382051925</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>모브플렉스 웰니스클럽 북가좌점</t>
+          <t>짐티피 연희점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>movflex@naver.com</t>
+          <t>gymtipi5@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1465-5212</t>
+          <t>0507-1411-0572</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 서대문구 응암로 118 C동 0층</t>
+          <t>서울특별시 서대문구 연희로25길 18 지하 1층(연희동, 대화 빌딩)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.movflex.co.kr</t>
+          <t>https://blog.naver.com/gymtipi5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,19 +1169,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsjq5zj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>211</v>
+        <v>505</v>
       </c>
       <c r="Q8" t="n">
-        <v>45</v>
+        <v>495</v>
       </c>
       <c r="R8" t="n">
-        <v>256</v>
+        <v>1000</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1920908511</t>
+          <t>1530671650</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920908511</t>
+          <t>https://m.place.naver.com/place/1530671650</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엠베이스짐 가재울점</t>
+          <t>피티루트 홍제 무악재점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mbasegym@naver.com</t>
+          <t>hayama89@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1442-2222</t>
+          <t>0507-1343-0653</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 수색로 56 성공타워 6층 608호 엠베이스짐</t>
+          <t>서울특별시 서대문구 통일로 360 보하빌딩 6층 피티루트</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/pt_root</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,7 +1258,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1292,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc3rb1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>279</v>
       </c>
       <c r="R9" t="n">
-        <v>30</v>
+        <v>404</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37294107</t>
+          <t>1191919965</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37294107</t>
+          <t>https://m.place.naver.com/place/1191919965</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스타칼리휘트니스 연희점</t>
+          <t>크로스핏 런신촌</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>starkalibest@naver.com</t>
+          <t>projectfithouse@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1328-4477</t>
+          <t>0507-1365-1825</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 82 브라운스톤 연희 B1</t>
+          <t>서울특별시 서대문구 연세로9길 37 지하 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.projectrun.co.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,27 +1352,23 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5y1bb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>276</v>
+        <v>193</v>
       </c>
       <c r="Q10" t="n">
-        <v>372</v>
+        <v>241</v>
       </c>
       <c r="R10" t="n">
-        <v>648</v>
+        <v>434</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1392,111 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>31044421</t>
+          <t>1720233681</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31044421</t>
+          <t>https://m.place.naver.com/place/1720233681</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>수 피티 연희점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lovedaisy78@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1438-8791</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>서울특별시 서대문구 연희로 81-21 6층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sufit.ness</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>147</v>
+      </c>
+      <c r="R11" t="n">
+        <v>266</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1060397560</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1060397560</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서대문_PT.xlsx
+++ b/naver-place-crawler/results_health/서대문_PT.xlsx
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>홀리핏 신촌점</t>
+          <t>이태원짐 서대문구청점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ycy06177@naver.com</t>
+          <t>itaewongym2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1409-9915</t>
+          <t>0507-1335-4180</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물1길 16 1층~4층</t>
+          <t>서울특별시 서대문구 연희로 286 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ycy06177</t>
+          <t>https://blog.naver.com/itaewongym2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="Q4" t="n">
-        <v>1095</v>
+        <v>210</v>
       </c>
       <c r="R4" t="n">
-        <v>1762</v>
+        <v>854</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1703343634</t>
+          <t>1853970001</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1703343634</t>
+          <t>https://m.place.naver.com/place/1853970001</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="Q5" t="n">
         <v>1525</v>
       </c>
       <c r="R5" t="n">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이태원짐 서대문구청점</t>
+          <t>홀리핏 신촌점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>itaewongym2@naver.com</t>
+          <t>ycy06177@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1335-4180</t>
+          <t>0507-1409-9915</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 286 2층</t>
+          <t>서울특별시 서대문구 명물1길 16 1층~4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewongym2</t>
+          <t>https://blog.naver.com/ycy06177</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>643</v>
+        <v>667</v>
       </c>
       <c r="Q6" t="n">
-        <v>210</v>
+        <v>1095</v>
       </c>
       <c r="R6" t="n">
-        <v>853</v>
+        <v>1762</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1853970001</t>
+          <t>1703343634</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853970001</t>
+          <t>https://m.place.naver.com/place/1703343634</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1098,10 +1098,10 @@
         <v>655</v>
       </c>
       <c r="Q7" t="n">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="R7" t="n">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/서대문_PT.xlsx
+++ b/naver-place-crawler/results_health/서대문_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessm17</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itbodyfitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,23 +694,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qwpv</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -722,10 +726,10 @@
         <v>831</v>
       </c>
       <c r="Q3" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="R3" t="n">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이태원짐 서대문구청점</t>
+          <t>홀리핏 신촌점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>itaewongym2@naver.com</t>
+          <t>ycy06177@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1335-4180</t>
+          <t>0507-1409-9915</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 286 2층</t>
+          <t>서울특별시 서대문구 명물1길 16 1층~4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewongym2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,20 +792,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4c2rj</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>644</v>
+        <v>667</v>
       </c>
       <c r="Q4" t="n">
-        <v>210</v>
+        <v>1101</v>
       </c>
       <c r="R4" t="n">
-        <v>854</v>
+        <v>1768</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1853970001</t>
+          <t>1703343634</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853970001</t>
+          <t>https://m.place.naver.com/place/1703343634</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 무악재점</t>
+          <t>이태원짐 서대문구청점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1986fitness5@naver.com</t>
+          <t>itaewongym2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1443-1986</t>
+          <t>0507-1335-4180</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 339 B층 301호</t>
+          <t>서울특별시 서대문구 연희로 286 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,20 +890,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fh3o</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1963</v>
+        <v>644</v>
       </c>
       <c r="Q5" t="n">
-        <v>1525</v>
+        <v>210</v>
       </c>
       <c r="R5" t="n">
-        <v>3488</v>
+        <v>854</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1220265026</t>
+          <t>1853970001</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220265026</t>
+          <t>https://m.place.naver.com/place/1853970001</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>홀리핏 신촌점</t>
+          <t>1986피트니스 헬스PT 무악재점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ycy06177@naver.com</t>
+          <t>1986fitness5@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1409-9915</t>
+          <t>0507-1443-1986</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 명물1길 16 1층~4층</t>
+          <t>서울특별시 서대문구 통일로 339 B층 301호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ycy06177</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,20 +988,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4szvi</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>667</v>
+        <v>1964</v>
       </c>
       <c r="Q6" t="n">
-        <v>1095</v>
+        <v>1533</v>
       </c>
       <c r="R6" t="n">
-        <v>1762</v>
+        <v>3497</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1703343634</t>
+          <t>1220265026</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1703343634</t>
+          <t>https://m.place.naver.com/place/1220265026</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>셀프메이드짐 연희</t>
+          <t>바디채널&amp;히트35 신촌이대역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>selfmadegym2@naver.com</t>
+          <t>bodych36@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1360-5190</t>
+          <t>0507-1473-2117</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 185 B1 셀프메이드짐 연희</t>
+          <t>서울특별시 서대문구 신촌로 155 해암빌딩 3층, 4층 바디채널</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/selfmadegym2/223397334694</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,20 +1086,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46zbh</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>655</v>
+        <v>572</v>
       </c>
       <c r="Q7" t="n">
-        <v>1752</v>
+        <v>338</v>
       </c>
       <c r="R7" t="n">
-        <v>2407</v>
+        <v>910</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1382051925</t>
+          <t>1485878804</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382051925</t>
+          <t>https://m.place.naver.com/place/1485878804</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>짐티피 연희점</t>
+          <t>수 피티 연희점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gymtipi5@naver.com</t>
+          <t>lovedaisy78@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1411-0572</t>
+          <t>0507-1438-8791</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로25길 18 지하 1층(연희동, 대화 빌딩)</t>
+          <t>서울특별시 서대문구 연희로 81-21 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymtipi5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,20 +1184,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qp0x</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>505</v>
+        <v>119</v>
       </c>
       <c r="Q8" t="n">
-        <v>495</v>
+        <v>147</v>
       </c>
       <c r="R8" t="n">
-        <v>1000</v>
+        <v>266</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1530671650</t>
+          <t>1060397560</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1530671650</t>
+          <t>https://m.place.naver.com/place/1060397560</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,34 +1250,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피티루트 홍제 무악재점</t>
+          <t>모브플렉스 웰니스클럽 북가좌점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hayama89@naver.com</t>
+          <t>movflex@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1343-0653</t>
+          <t>0507-1465-5212</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 통일로 360 보하빌딩 6층 피티루트</t>
+          <t>서울 서대문구 응암로 118 C동 0층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pt_root</t>
+          <t>https://www.movflex.co.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1268,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsjq5zj</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="Q9" t="n">
-        <v>279</v>
+        <v>45</v>
       </c>
       <c r="R9" t="n">
-        <v>404</v>
+        <v>256</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1191919965</t>
+          <t>1920908511</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1191919965</t>
+          <t>https://m.place.naver.com/place/1920908511</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>크로스핏 런신촌</t>
+          <t>엠베이스짐 가재울점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>projectfithouse@naver.com</t>
+          <t>mbasegym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1365-1825</t>
+          <t>0507-1442-2222</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연세로9길 37 지하 1층</t>
+          <t>서울특별시 서대문구 수색로 56 성공타워 6층 608호 엠베이스짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.projectrun.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,20 +1380,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc3rb1</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>193</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>241</v>
+        <v>17</v>
       </c>
       <c r="R10" t="n">
-        <v>434</v>
+        <v>30</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1720233681</t>
+          <t>37294107</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720233681</t>
+          <t>https://m.place.naver.com/place/37294107</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,34 +1441,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>수 피티 연희점</t>
+          <t>스타칼리휘트니스 연희점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lovedaisy78@naver.com</t>
+          <t>starkalibest@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1438-8791</t>
+          <t>0507-1328-4477</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 서대문구 연희로 81-21 6층</t>
+          <t>서울특별시 서대문구 연희로 82 브라운스톤 연희 B1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sufit.ness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1446,7 +1478,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1456,13 +1488,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5y1bb</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1471,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>119</v>
+        <v>276</v>
       </c>
       <c r="Q11" t="n">
-        <v>147</v>
+        <v>372</v>
       </c>
       <c r="R11" t="n">
-        <v>266</v>
+        <v>648</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1060397560</t>
+          <t>31044421</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060397560</t>
+          <t>https://m.place.naver.com/place/31044421</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/서대문_PT.xlsx
+++ b/naver-place-crawler/results_health/서대문_PT.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitnessm17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/itbodyfitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,27 +694,23 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qwpv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -748,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -782,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ycy06177</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,24 +788,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4c2rj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -824,10 +816,10 @@
         <v>667</v>
       </c>
       <c r="Q4" t="n">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="R4" t="n">
-        <v>1768</v>
+        <v>1772</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -880,7 +872,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/itaewongym2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,24 +882,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fh3o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -944,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -978,7 +966,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/1986fitness5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,24 +976,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4szvi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1020,10 +1004,10 @@
         <v>1964</v>
       </c>
       <c r="Q6" t="n">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="R6" t="n">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1060,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bodych36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,24 +1070,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46zbh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1140,7 +1120,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1154,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sufit.ness</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,7 +1164,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1194,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qp0x</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1238,7 +1214,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1312,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1346,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mbasegym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,24 +1356,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc3rb1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1434,7 +1406,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1468,17 +1440,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_gknKT/chat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1488,14 +1460,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5y1bb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>O</t>
@@ -1532,7 +1500,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
